--- a/D-00002/operation-mapping_D-00002.xlsx
+++ b/D-00002/operation-mapping_D-00002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Husband\github\iniciativas\D-00002\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F0A7911-39BD-4C51-A659-DDF8E239BF38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F83C3F9-A97D-4C13-8B18-7F91CCB5445E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
   <si>
     <t xml:space="preserve">API                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
   </si>
@@ -76,6 +76,21 @@
   </si>
   <si>
     <t>GET</t>
+  </si>
+  <si>
+    <t>BS</t>
+  </si>
+  <si>
+    <t>API BS Customer Offer V1</t>
+  </si>
+  <si>
+    <t>POST</t>
+  </si>
+  <si>
+    <t>/customer-offers/initiate</t>
+  </si>
+  <si>
+    <t>Inicializar</t>
   </si>
 </sst>
 </file>
@@ -393,11 +408,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="41.109375" customWidth="1"/>
-    <col min="6" max="6" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -467,6 +482,29 @@
       </c>
       <c r="G3" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
